--- a/data/service-prices.xlsx
+++ b/data/service-prices.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamd\Github\maro_web\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stano\Documents\mobilflex\dzuris.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F29A00DE-EEC9-4F07-A4D7-3B3CC61C8A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A230A04-859D-4AEB-B6F9-B88C2D149112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{E889351A-8D47-49F3-90BB-9B5B0FF2FD64}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{E889351A-8D47-49F3-90BB-9B5B0FF2FD64}"/>
   </bookViews>
   <sheets>
     <sheet name="iphone" sheetId="1" r:id="rId1"/>
-    <sheet name="samsung" sheetId="2" r:id="rId2"/>
+    <sheet name="samsung" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
   <si>
     <t>ProductName</t>
   </si>
@@ -45,9 +45,6 @@
     <t>displej</t>
   </si>
   <si>
-    <t>iphone-6-6S-plus</t>
-  </si>
-  <si>
     <t>bateria</t>
   </si>
   <si>
@@ -102,7 +99,34 @@
     <t>inyproblem</t>
   </si>
   <si>
-    <t>iphone-6-6S</t>
+    <t>galaxy-a</t>
+  </si>
+  <si>
+    <t>SubCategory</t>
+  </si>
+  <si>
+    <t>galaxy-a-02.json</t>
+  </si>
+  <si>
+    <t>galaxy-a-02s.json</t>
+  </si>
+  <si>
+    <t>galaxy-m</t>
+  </si>
+  <si>
+    <t>galaxy-m-11.json</t>
+  </si>
+  <si>
+    <t>galaxy-m12</t>
+  </si>
+  <si>
+    <t>backglass</t>
+  </si>
+  <si>
+    <t>iphone-6-6S-plus.json</t>
+  </si>
+  <si>
+    <t>"Zadarmo"</t>
   </si>
 </sst>
 </file>
@@ -147,10 +171,10 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normálna" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -166,7 +190,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motív Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -462,132 +486,118 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1D3CA37-09CC-4DEA-ADDE-A1FEC67AF807}">
-  <dimension ref="A1:T3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="6.140625" customWidth="1"/>
-    <col min="16" max="16" width="11.5703125" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" customWidth="1"/>
-    <col min="19" max="19" width="12.5703125" customWidth="1"/>
-    <col min="20" max="20" width="13" customWidth="1"/>
-    <col min="21" max="21" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="17.88671875" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" customWidth="1"/>
+    <col min="3" max="22" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="T1" t="s">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2">
+        <v>45</v>
+      </c>
+      <c r="D2">
+        <v>29</v>
+      </c>
+      <c r="E2">
+        <v>30</v>
+      </c>
+      <c r="G2">
+        <v>45</v>
+      </c>
+      <c r="H2">
+        <v>28</v>
+      </c>
+      <c r="I2">
+        <v>28</v>
+      </c>
+      <c r="J2">
         <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>35</v>
-      </c>
-      <c r="C2">
-        <v>29</v>
-      </c>
-      <c r="D2">
-        <v>30</v>
-      </c>
-      <c r="E2">
-        <v>45</v>
-      </c>
-      <c r="F2">
-        <v>25</v>
-      </c>
-      <c r="G2">
-        <v>25</v>
-      </c>
-      <c r="H2">
-        <v>20</v>
-      </c>
-      <c r="I2">
-        <v>25</v>
-      </c>
-      <c r="J2">
-        <v>29</v>
       </c>
       <c r="K2">
         <v>25</v>
       </c>
       <c r="L2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M2">
         <v>25</v>
       </c>
       <c r="N2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="O2">
         <v>25</v>
@@ -596,18 +606,19 @@
         <v>25</v>
       </c>
       <c r="Q2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R2">
         <v>30</v>
       </c>
       <c r="S2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="T2">
+        <v>30</v>
+      </c>
+      <c r="U2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -616,81 +627,173 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FCBF4E4-2AFE-469F-BE5B-C014EDC8CB07}">
-  <dimension ref="A1:T1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{558A7059-3FBC-4BEF-BB0E-6977AF0BCB15}">
+  <dimension ref="A1:V5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="14" max="14" width="11.28515625" customWidth="1"/>
-    <col min="16" max="16" width="11.28515625" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="23" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="T1" t="s">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2">
+        <v>80</v>
+      </c>
+      <c r="D2">
+        <v>55</v>
+      </c>
+      <c r="E2">
+        <v>54</v>
+      </c>
+      <c r="F2">
+        <v>47</v>
+      </c>
+      <c r="T2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3">
+        <v>80</v>
+      </c>
+      <c r="D3">
+        <v>51</v>
+      </c>
+      <c r="E3">
+        <v>54</v>
+      </c>
+      <c r="F3">
+        <v>47</v>
+      </c>
+      <c r="T3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>83</v>
+      </c>
+      <c r="D4">
+        <v>49</v>
+      </c>
+      <c r="E4">
+        <v>54</v>
+      </c>
+      <c r="F4">
+        <v>47</v>
+      </c>
+      <c r="T4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>85</v>
+      </c>
+      <c r="D5">
+        <v>49</v>
+      </c>
+      <c r="E5">
+        <v>56</v>
+      </c>
+      <c r="F5">
+        <v>47</v>
+      </c>
+      <c r="T5">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
